--- a/Manba  IMF, World Bank, EBA, O‘zbekiston Respublikasi Markaziy banki ma’lumotlari asosida muallif tomonidan tayyorlandi..xlsx
+++ b/Manba  IMF, World Bank, EBA, O‘zbekiston Respublikasi Markaziy banki ma’lumotlari asosida muallif tomonidan tayyorlandi..xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\maqsudbek\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSPanel\home\maqsudbek\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Лист4" sheetId="4" r:id="rId4"/>
+    <sheet name="Лист5" sheetId="5" r:id="rId5"/>
+    <sheet name="Лист6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>Mamlakat / Mintaqa</t>
   </si>
@@ -135,12 +138,75 @@
   <si>
     <t>Jahon bo‘yicha jami</t>
   </si>
+  <si>
+    <t>To'lovga qobiliyatsizlik</t>
+  </si>
+  <si>
+    <t>Moliyaviy savodsizlik</t>
+  </si>
+  <si>
+    <t>Kredit maqsadsiz ishlatilishi</t>
+  </si>
+  <si>
+    <t>Kafolat yetishmasligi</t>
+  </si>
+  <si>
+    <t>Yomon monitoring</t>
+  </si>
+  <si>
+    <t>Makroiqtisodiy beqarorlik</t>
+  </si>
+  <si>
+    <t>Huquqly tartibotdagi muammolar</t>
+  </si>
+  <si>
+    <t>Garov ta'minotining yetarli emasligi</t>
+  </si>
+  <si>
+    <t>Kredit oluvchilarning moliyaviy holati zaifligi</t>
+  </si>
+  <si>
+    <t>Tijorat risklar va bozor o'zgarishlari</t>
+  </si>
+  <si>
+    <t>Kredit monitoringining sustligi</t>
+  </si>
+  <si>
+    <t>Tijorat banklari faoliyatida muammoli kreditlar paydo bo'lishiga ta'sir etuvchi omillar</t>
+  </si>
+  <si>
+    <t>Foiz Stavkalari yuqoriligi</t>
+  </si>
+  <si>
+    <t>Mintaqa / Davlat</t>
+  </si>
+  <si>
+    <t>2023-yil (%)</t>
+  </si>
+  <si>
+    <t>2024-yil (%)</t>
+  </si>
+  <si>
+    <t>2025-yil (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yevropa Ittifoqi </t>
+  </si>
+  <si>
+    <t>AQSh</t>
+  </si>
+  <si>
+    <t>Rivojlanayotgan davlatlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osiyo </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,6 +239,21 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -182,7 +263,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -251,11 +332,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -284,9 +418,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -302,7 +456,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -402,8 +556,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -422,8 +577,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -442,8 +598,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -471,7 +628,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -536,6 +693,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-FB05-45C1-BF6A-B28C154C54A4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -578,8 +740,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -598,8 +761,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -618,8 +782,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -647,7 +812,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -712,6 +877,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-FB05-45C1-BF6A-B28C154C54A4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -754,8 +924,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -774,8 +945,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -794,8 +966,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -823,7 +996,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -888,6 +1061,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-FB05-45C1-BF6A-B28C154C54A4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -930,8 +1108,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -950,8 +1129,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -970,8 +1150,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -999,7 +1180,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1064,6 +1245,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-FB05-45C1-BF6A-B28C154C54A4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -1106,8 +1292,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1126,8 +1313,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1146,8 +1334,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1175,7 +1364,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1240,6 +1429,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000013-FB05-45C1-BF6A-B28C154C54A4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
@@ -1282,8 +1476,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1302,8 +1497,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1322,8 +1518,9 @@
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                  <c15:layout/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-FB05-45C1-BF6A-B28C154C54A4}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -1351,7 +1548,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1416,6 +1613,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000017-FB05-45C1-BF6A-B28C154C54A4}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1466,7 +1668,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="454740576"/>
@@ -1525,7 +1727,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="454738944"/>
@@ -1542,7 +1744,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1568,7 +1769,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1601,7 +1802,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1613,7 +1814,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -1653,7 +1854,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1679,7 +1879,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1801,6 +2001,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-00B6-4C83-A9E3-0E39A22E396F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1874,6 +2079,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-00B6-4C83-A9E3-0E39A22E396F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1947,6 +2157,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-00B6-4C83-A9E3-0E39A22E396F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -2020,6 +2235,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-00B6-4C83-A9E3-0E39A22E396F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -2093,6 +2313,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-00B6-4C83-A9E3-0E39A22E396F}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2143,7 +2368,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="404255472"/>
@@ -2202,7 +2427,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="404242960"/>
@@ -2254,7 +2479,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2287,7 +2512,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2299,7 +2524,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -2404,6 +2629,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-827B-43FD-8035-246C91473991}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2491,6 +2721,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-827B-43FD-8035-246C91473991}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2578,6 +2813,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-827B-43FD-8035-246C91473991}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -2665,6 +2905,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-827B-43FD-8035-246C91473991}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -2752,6 +2997,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-827B-43FD-8035-246C91473991}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
@@ -2839,6 +3089,11 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-827B-43FD-8035-246C91473991}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2888,7 +3143,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="629079344"/>
@@ -2947,7 +3202,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="629068464"/>
@@ -2990,7 +3245,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3023,7 +3278,1806 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1320" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Muammoli kreditlar paydo bo'lishiga ta'sir etuvchi omillar tahlili</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1320" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000E-A7D7-49F2-A992-E7C84464DF5D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000C-A7D7-49F2-A992-E7C84464DF5D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000A-A7D7-49F2-A992-E7C84464DF5D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-A7D7-49F2-A992-E7C84464DF5D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-A7D7-49F2-A992-E7C84464DF5D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A7D7-49F2-A992-E7C84464DF5D}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист4!$A$4:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>To'lovga qobiliyatsizlik</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Moliyaviy savodsizlik</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Kredit maqsadsiz ishlatilishi</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Kafolat yetishmasligi</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Yomon monitoring</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Makroiqtisodiy beqarorlik</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист4!$B$4:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A7D7-49F2-A992-E7C84464DF5D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="1806550719"/>
+        <c:axId val="1806553215"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="1806550719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1806553215"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1806553215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1806550719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.3989938757655297E-2"/>
+          <c:y val="5.0925925925925923E-2"/>
+          <c:w val="0.53888888888888886"/>
+          <c:h val="0.89814814814814814"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F41C-4ED8-A44D-1F2F54FEF3A1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-F41C-4ED8-A44D-1F2F54FEF3A1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист5!$B$3:$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Foiz Stavkalari yuqoriligi</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Huquqly tartibotdagi muammolar</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Garov ta'minotining yetarli emasligi</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Kredit oluvchilarning moliyaviy holati zaifligi</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tijorat risklar va bozor o'zgarishlari</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Kredit monitoringining sustligi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист5!$C$3:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F41C-4ED8-A44D-1F2F54FEF3A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.55853565179352582"/>
+          <c:y val="0.10069116360454942"/>
+          <c:w val="0.43868657042869641"/>
+          <c:h val="0.77083989501312333"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист6!$B$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Rivojlanayotgan davlatlar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист6!$C$3:$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2023-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2024-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025-yil (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист6!$C$7:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.03</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2E11-45C5-B9BB-57F521E21EB7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист6!$B$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Osiyo </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.3333333333333333E-2"/>
+                  <c:y val="-0.14351851851851857"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.3333333333333333E-2"/>
+                  <c:y val="-0.14351851851851852"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.8888888888888785E-2"/>
+                  <c:y val="-0.10185185185185189"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист6!$C$3:$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2023-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2024-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025-yil (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист6!$C$6:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2E11-45C5-B9BB-57F521E21EB7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист6!$B$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>AQSh</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.3333333333333332E-3"/>
+                  <c:y val="-0.11574074074074074"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.6666666666666666E-2"/>
+                  <c:y val="-0.12500000000000006"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="1.6666666666666566E-2"/>
+                  <c:y val="-0.12500000000000008"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист6!$C$3:$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2023-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2024-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025-yil (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист6!$C$5:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2E11-45C5-B9BB-57F521E21EB7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Лист6!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Yevropa Ittifoqi </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.5000000000000001E-2"/>
+                  <c:y val="-8.3333333333333329E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.5000000000000001E-2"/>
+                  <c:y val="-0.10185185185185189"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="7.2222222222222215E-2"/>
+                  <c:y val="-3.7037037037037035E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-2E11-45C5-B9BB-57F521E21EB7}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Лист6!$C$3:$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>2023-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2024-yil (%)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2025-yil (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист6!$C$4:$E$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2E11-45C5-B9BB-57F521E21EB7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="1640967311"/>
+        <c:axId val="1640974799"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="1640967311"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1640974799"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1640974799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1640967311"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3154,6 +5208,123 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent5"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
@@ -4143,6 +6314,1595 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="39000">
+            <a:schemeClr val="lt1"/>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="lt1">
+              <a:lumMod val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="pct75">
+        <a:fgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+    <cs:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="dk1">
+                <a:lumMod val="95000"/>
+                <a:lumOff val="5000"/>
+                <a:alpha val="42000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="75000"/>
+                <a:alpha val="36000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+          <a:alpha val="39000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4724,6 +8484,111 @@
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>312420</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>624840</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>179070</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -5183,7 +9048,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>23</v>
       </c>
@@ -5450,4 +9315,231 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A4:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="10">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="10">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="10">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="10">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="10">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="10">
+        <v>0.13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="37.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="10">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="10">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="10">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="27.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="D4" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="E4" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D5" s="16">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E5" s="16">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D6" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="E6" s="16">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D7" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0.03</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>